--- a/Gantt chart.xlsx
+++ b/Gantt chart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27726"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Courses\2810ICT\2024\2810-7810-workspace\Group_Project\M1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gregory\Desktop\st_m1\Milestone1_Group52\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9675C1-8042-4DA2-BC81-E829931B8A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B20DDC-BEED-4215-ACAB-1A3CACE96739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1665" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Planner" sheetId="1" r:id="rId1"/>
@@ -37,87 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>PERIODS</t>
-  </si>
-  <si>
-    <t>Activity 01</t>
-  </si>
-  <si>
-    <t>Activity 02</t>
-  </si>
-  <si>
-    <t>Activity 03</t>
-  </si>
-  <si>
-    <t>Activity 04</t>
-  </si>
-  <si>
-    <t>Activity 05</t>
-  </si>
-  <si>
-    <t>Activity 06</t>
-  </si>
-  <si>
-    <t>Activity 07</t>
-  </si>
-  <si>
-    <t>Activity 08</t>
-  </si>
-  <si>
-    <t>Activity 09</t>
-  </si>
-  <si>
-    <t>Activity 10</t>
-  </si>
-  <si>
-    <t>Activity 11</t>
-  </si>
-  <si>
-    <t>Activity 12</t>
-  </si>
-  <si>
-    <t>Activity 13</t>
-  </si>
-  <si>
-    <t>Activity 14</t>
-  </si>
-  <si>
-    <t>Activity 15</t>
-  </si>
-  <si>
-    <t>Activity 16</t>
-  </si>
-  <si>
-    <t>Activity 17</t>
-  </si>
-  <si>
-    <t>Activity 18</t>
-  </si>
-  <si>
-    <t>Activity 19</t>
-  </si>
-  <si>
-    <t>Activity 20</t>
-  </si>
-  <si>
-    <t>Activity 21</t>
-  </si>
-  <si>
-    <t>Activity 22</t>
-  </si>
-  <si>
-    <t>Activity 23</t>
-  </si>
-  <si>
-    <t>Activity 24</t>
-  </si>
-  <si>
-    <t>Activity 25</t>
-  </si>
-  <si>
-    <t>Activity 26</t>
   </si>
   <si>
     <r>
@@ -207,36 +129,6 @@
     <t>Plan Duration</t>
   </si>
   <si>
-    <t>Activity 27</t>
-  </si>
-  <si>
-    <t>Activity 28</t>
-  </si>
-  <si>
-    <t>Activity 29</t>
-  </si>
-  <si>
-    <t>Activity 30</t>
-  </si>
-  <si>
-    <t>Activity 31</t>
-  </si>
-  <si>
-    <t>Activity 32</t>
-  </si>
-  <si>
-    <t>Activity 33</t>
-  </si>
-  <si>
-    <t>Activity 34</t>
-  </si>
-  <si>
-    <t>Activity 35</t>
-  </si>
-  <si>
-    <t>Project Title</t>
-  </si>
-  <si>
     <t>Plan
 Start</t>
   </si>
@@ -262,13 +154,115 @@
   </si>
   <si>
     <t>Activity No. and Name</t>
+  </si>
+  <si>
+    <t>2 Develop Project Plan</t>
+  </si>
+  <si>
+    <t>2.1 Define Project Objectives</t>
+  </si>
+  <si>
+    <t>2.2 Identify Project Stakeholders</t>
+  </si>
+  <si>
+    <t>2.3 Define Project Scope</t>
+  </si>
+  <si>
+    <t>2.4 Develop WBS</t>
+  </si>
+  <si>
+    <t>2.5 Activity Definition Estimate</t>
+  </si>
+  <si>
+    <t>2.6 Gantt Chart Preperation</t>
+  </si>
+  <si>
+    <t>2.7 Develop Software Design Document</t>
+  </si>
+  <si>
+    <t>2.7.1 System Vision</t>
+  </si>
+  <si>
+    <t>2.7.1.1 Problem Background</t>
+  </si>
+  <si>
+    <t>2.7.1.2 System Capabilities Overview</t>
+  </si>
+  <si>
+    <t>2.7.1.3 Benefit Analysis</t>
+  </si>
+  <si>
+    <t>2.7.2 Requirements</t>
+  </si>
+  <si>
+    <t>2.7.2.1 User Requirements</t>
+  </si>
+  <si>
+    <t>2.7.2.2 Software Requirements</t>
+  </si>
+  <si>
+    <t>2.7.2.3 Use Case Diagram</t>
+  </si>
+  <si>
+    <t>2.7.2.4 Use Cases</t>
+  </si>
+  <si>
+    <t>2.7.3 Software Design and System Components</t>
+  </si>
+  <si>
+    <t>2.7.3.1 Software Design</t>
+  </si>
+  <si>
+    <t>2.7.3.2 System Components</t>
+  </si>
+  <si>
+    <t>2.7.3.2.1 Functions</t>
+  </si>
+  <si>
+    <t>2.7.3.2.2 Data Structures/Sources</t>
+  </si>
+  <si>
+    <t>2.7.3.2.3 Detailed Design</t>
+  </si>
+  <si>
+    <t>2.7.4 UI Design</t>
+  </si>
+  <si>
+    <t>2.7.4.1 Structural Design</t>
+  </si>
+  <si>
+    <t>2.7.4.2 Visual Design</t>
+  </si>
+  <si>
+    <t>3.1 Develop Software Components</t>
+  </si>
+  <si>
+    <t>3.2 Integrate Software Components</t>
+  </si>
+  <si>
+    <t>3.3 Perform Initial Testing</t>
+  </si>
+  <si>
+    <t>4.1 Status Reports</t>
+  </si>
+  <si>
+    <t>4.2 Update Plans</t>
+  </si>
+  <si>
+    <t>5.1 Final Performance Review</t>
+  </si>
+  <si>
+    <t>5.2 Prepare Final Report</t>
+  </si>
+  <si>
+    <t>Nutrition App Development</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1" tint="0.24994659260841701"/>
@@ -378,8 +372,23 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Corbel"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -419,6 +428,11 @@
       <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -565,7 +579,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -599,9 +613,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="8">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="11" fillId="6" borderId="1" xfId="13">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -638,6 +649,33 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="10" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="12">
       <alignment vertical="center"/>
     </xf>
@@ -650,32 +688,14 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="10" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="10" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -1092,91 +1112,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:67" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.85">
-      <c r="B1" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="10"/>
+      <c r="C1" s="37" t="s">
+        <v>46</v>
+      </c>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
     </row>
     <row r="2" spans="2:67" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" s="12">
-        <v>1</v>
-      </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="35"/>
-      <c r="AE2" s="35"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="36"/>
-      <c r="AH2" s="17"/>
-      <c r="AI2" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="AJ2" s="20"/>
-      <c r="AK2" s="20"/>
-      <c r="AL2" s="20"/>
-      <c r="AM2" s="20"/>
-      <c r="AN2" s="20"/>
-      <c r="AO2" s="20"/>
-      <c r="AP2" s="20"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="11">
+        <v>1</v>
+      </c>
+      <c r="J2" s="12"/>
+      <c r="K2" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB2" s="30"/>
+      <c r="AC2" s="30"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="30"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="31"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ2" s="19"/>
+      <c r="AK2" s="19"/>
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="19"/>
+      <c r="AN2" s="19"/>
+      <c r="AO2" s="19"/>
+      <c r="AP2" s="19"/>
     </row>
     <row r="3" spans="2:67" s="9" customFormat="1" ht="39.950000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" s="18" t="s">
+      <c r="B3" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="17" t="s">
         <v>0</v>
       </c>
       <c r="I3" s="7"/>
@@ -1200,12 +1219,12 @@
       <c r="AA3" s="8"/>
     </row>
     <row r="4" spans="2:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="26"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
       <c r="H4" s="3">
         <v>1</v>
       </c>
@@ -1388,450 +1407,790 @@
       </c>
     </row>
     <row r="5" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="23" t="s">
-        <v>1</v>
+      <c r="B5" s="36" t="s">
+        <v>13</v>
       </c>
       <c r="C5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="22">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G5" s="21">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <v>3</v>
+      </c>
+      <c r="G6" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>3</v>
+      </c>
+      <c r="G7" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>3</v>
+      </c>
+      <c r="G8" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="5">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="23" t="s">
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5">
+        <v>2</v>
+      </c>
+      <c r="F10" s="5">
+        <v>2</v>
+      </c>
+      <c r="G10" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
         <v>3</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="23" t="s">
+      <c r="E11" s="5">
+        <v>2</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2</v>
+      </c>
+      <c r="G11" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5">
         <v>4</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="23" t="s">
+      <c r="D12" s="5">
+        <v>6</v>
+      </c>
+      <c r="E12" s="5">
         <v>5</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="23" t="s">
+      <c r="F12" s="5">
+        <v>7</v>
+      </c>
+      <c r="G12" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="5">
+        <v>4</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5">
+        <v>5</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+      <c r="G13" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="5">
+        <v>4</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5">
+        <v>5</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="6">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>7</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
+        <v>7</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5">
+        <v>5</v>
+      </c>
+      <c r="D17" s="5">
+        <v>2</v>
+      </c>
+      <c r="E17" s="5">
+        <v>5</v>
+      </c>
+      <c r="F17" s="5">
         <v>6</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="23" t="s">
+      <c r="G17" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="5">
+        <v>5</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5">
+        <v>5</v>
+      </c>
+      <c r="F18" s="5">
+        <v>1</v>
+      </c>
+      <c r="G18" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="5">
+        <v>5</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5">
         <v>7</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="23" t="s">
+      <c r="F19" s="5">
+        <v>4</v>
+      </c>
+      <c r="G19" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="5">
+        <v>5</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5">
+        <v>11</v>
+      </c>
+      <c r="F20" s="5">
+        <v>1</v>
+      </c>
+      <c r="G20" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="5">
+        <v>6</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5">
+        <v>9</v>
+      </c>
+      <c r="F21" s="5">
+        <v>1</v>
+      </c>
+      <c r="G21" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="5">
+        <v>6</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2</v>
+      </c>
+      <c r="E22" s="5">
+        <v>7</v>
+      </c>
+      <c r="F22" s="5">
+        <v>6</v>
+      </c>
+      <c r="G22" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="5">
+        <v>6</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5">
+        <v>10</v>
+      </c>
+      <c r="F23" s="5">
+        <v>3</v>
+      </c>
+      <c r="G23" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="5">
+        <v>6</v>
+      </c>
+      <c r="D24" s="5">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5">
+        <v>7</v>
+      </c>
+      <c r="F24" s="5">
+        <v>3</v>
+      </c>
+      <c r="G24" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="5">
+        <v>7</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5">
+        <v>7</v>
+      </c>
+      <c r="F25" s="5">
+        <v>3</v>
+      </c>
+      <c r="G25" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="5">
+        <v>7</v>
+      </c>
+      <c r="D26" s="5">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5">
+        <v>10</v>
+      </c>
+      <c r="F26" s="5">
+        <v>2</v>
+      </c>
+      <c r="G26" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="5">
+        <v>7</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5">
         <v>8</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="23" t="s">
+      <c r="F27" s="5">
+        <v>2</v>
+      </c>
+      <c r="G27" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="5">
         <v>9</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="23" t="s">
+      <c r="D28" s="5">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5">
+        <v>8</v>
+      </c>
+      <c r="F28" s="5">
+        <v>4</v>
+      </c>
+      <c r="G28" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="5">
+        <v>9</v>
+      </c>
+      <c r="D29" s="5">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5">
+        <v>8</v>
+      </c>
+      <c r="F29" s="5">
+        <v>4</v>
+      </c>
+      <c r="G29" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="5">
+        <v>9</v>
+      </c>
+      <c r="D30" s="5">
+        <v>2</v>
+      </c>
+      <c r="E30" s="5">
+        <v>8</v>
+      </c>
+      <c r="F30" s="5">
+        <v>4</v>
+      </c>
+      <c r="G30" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="5">
         <v>12</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="23" t="s">
+      <c r="D31" s="5">
         <v>14</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="22">
+      <c r="G31" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="B32" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="5">
+        <v>26</v>
+      </c>
+      <c r="D32" s="5">
+        <v>6</v>
+      </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
-      <c r="G32" s="22">
+      <c r="G32" s="21">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
+    <row r="33" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="5">
+        <v>32</v>
+      </c>
+      <c r="D33" s="5">
+        <v>4</v>
+      </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="22">
+      <c r="G33" s="21">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
+    <row r="34" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5">
+        <v>39</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1</v>
+      </c>
+      <c r="F34" s="5">
+        <v>11</v>
+      </c>
+      <c r="G34" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="5">
+        <v>12</v>
+      </c>
+      <c r="D35" s="5">
+        <v>28</v>
+      </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
-      <c r="G35" s="22">
+      <c r="G35" s="21">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
+    <row r="36" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="5">
+        <v>32</v>
+      </c>
+      <c r="D36" s="5">
+        <v>4</v>
+      </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
-      <c r="G36" s="22">
+      <c r="G36" s="21">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
+    <row r="37" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="5">
+        <v>36</v>
+      </c>
+      <c r="D37" s="5">
+        <v>4</v>
+      </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="22">
+      <c r="G37" s="21">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="23" t="s">
-        <v>39</v>
-      </c>
+    <row r="38" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="22"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
-      <c r="G38" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="23" t="s">
-        <v>40</v>
-      </c>
+      <c r="G38" s="21"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="38"/>
+      <c r="O38" s="38"/>
+      <c r="P38" s="38"/>
+      <c r="Q38" s="38"/>
+      <c r="R38" s="38"/>
+      <c r="S38" s="38"/>
+      <c r="T38" s="38"/>
+      <c r="U38" s="38"/>
+      <c r="V38" s="38"/>
+      <c r="W38" s="38"/>
+      <c r="X38" s="38"/>
+      <c r="Y38" s="38"/>
+      <c r="Z38" s="38"/>
+      <c r="AA38" s="38"/>
+      <c r="AB38" s="38"/>
+      <c r="AC38" s="38"/>
+      <c r="AD38" s="38"/>
+      <c r="AE38" s="38"/>
+      <c r="AF38" s="38"/>
+      <c r="AG38" s="38"/>
+      <c r="AH38" s="38"/>
+      <c r="AI38" s="38"/>
+      <c r="AJ38" s="38"/>
+      <c r="AK38" s="38"/>
+      <c r="AL38" s="38"/>
+      <c r="AM38" s="38"/>
+      <c r="AN38" s="38"/>
+      <c r="AO38" s="38"/>
+      <c r="AP38" s="38"/>
+      <c r="AQ38" s="38"/>
+      <c r="AR38" s="38"/>
+      <c r="AS38" s="38"/>
+      <c r="AT38" s="38"/>
+      <c r="AU38" s="38"/>
+      <c r="AV38" s="38"/>
+      <c r="AW38" s="38"/>
+      <c r="AX38" s="38"/>
+      <c r="AY38" s="38"/>
+      <c r="AZ38" s="38"/>
+      <c r="BA38" s="38"/>
+      <c r="BB38" s="38"/>
+      <c r="BC38" s="38"/>
+      <c r="BD38" s="38"/>
+      <c r="BE38" s="38"/>
+      <c r="BF38" s="38"/>
+      <c r="BG38" s="38"/>
+      <c r="BH38" s="38"/>
+      <c r="BI38" s="38"/>
+      <c r="BJ38" s="38"/>
+      <c r="BK38" s="38"/>
+      <c r="BL38" s="38"/>
+      <c r="BM38" s="38"/>
+      <c r="BN38" s="38"/>
+      <c r="BO38" s="38"/>
+    </row>
+    <row r="39" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="22"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
-      <c r="G39" s="22">
-        <v>0</v>
-      </c>
+      <c r="G39" s="21"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="38"/>
+      <c r="M39" s="38"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="38"/>
+      <c r="P39" s="38"/>
+      <c r="Q39" s="38"/>
+      <c r="R39" s="38"/>
+      <c r="S39" s="38"/>
+      <c r="T39" s="38"/>
+      <c r="U39" s="38"/>
+      <c r="V39" s="38"/>
+      <c r="W39" s="38"/>
+      <c r="X39" s="38"/>
+      <c r="Y39" s="38"/>
+      <c r="Z39" s="38"/>
+      <c r="AA39" s="38"/>
+      <c r="AB39" s="38"/>
+      <c r="AC39" s="38"/>
+      <c r="AD39" s="38"/>
+      <c r="AE39" s="38"/>
+      <c r="AF39" s="38"/>
+      <c r="AG39" s="38"/>
+      <c r="AH39" s="38"/>
+      <c r="AI39" s="38"/>
+      <c r="AJ39" s="38"/>
+      <c r="AK39" s="38"/>
+      <c r="AL39" s="38"/>
+      <c r="AM39" s="38"/>
+      <c r="AN39" s="38"/>
+      <c r="AO39" s="38"/>
+      <c r="AP39" s="38"/>
+      <c r="AQ39" s="38"/>
+      <c r="AR39" s="38"/>
+      <c r="AS39" s="38"/>
+      <c r="AT39" s="38"/>
+      <c r="AU39" s="38"/>
+      <c r="AV39" s="38"/>
+      <c r="AW39" s="38"/>
+      <c r="AX39" s="38"/>
+      <c r="AY39" s="38"/>
+      <c r="AZ39" s="38"/>
+      <c r="BA39" s="38"/>
+      <c r="BB39" s="38"/>
+      <c r="BC39" s="38"/>
+      <c r="BD39" s="38"/>
+      <c r="BE39" s="38"/>
+      <c r="BF39" s="38"/>
+      <c r="BG39" s="38"/>
+      <c r="BH39" s="38"/>
+      <c r="BI39" s="38"/>
+      <c r="BJ39" s="38"/>
+      <c r="BK39" s="38"/>
+      <c r="BL39" s="38"/>
+      <c r="BM39" s="38"/>
+      <c r="BN39" s="38"/>
+      <c r="BO39" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="K2:O2"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="V2:Y2"/>
-    <mergeCell ref="AA2:AG2"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="V2:Y2"/>
+    <mergeCell ref="AA2:AG2"/>
   </mergeCells>
   <conditionalFormatting sqref="H4:BO4">
     <cfRule type="expression" dxfId="8" priority="8">
@@ -1864,7 +2223,7 @@
       <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Project planner uses periods for intervals. Start=1 is period 1 and duration=5 means project spans 5 periods starting from start period. Enter data starting in B5 to update the chart" sqref="A1" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Type a value from 1 to 60 or select a period from the list-press  CANCEL, ALT+DOWN ARROW, then ENTER to select a value" prompt="Enter a period in the range of 1 to 60 or select a period from the list. Press ALT+DOWN ARROW to navigate the list, then ENTER to select a value" sqref="H2" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60"</formula1>
@@ -1881,12 +2240,11 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter actual start period in column E, starting with cell E5" sqref="E3:E4" xr:uid="{00000000-0002-0000-0000-00000B000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter actual duration period in column F, starting with cell F5" sqref="F3:F4" xr:uid="{00000000-0002-0000-0000-00000C000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter the percentage of project completed in column G, starting with cell G5" sqref="G3:G4" xr:uid="{00000000-0002-0000-0000-00000D000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Title of the project. Enter a new title in this cell. Highlight a period in H2. Chart legend is in J2 to AI2" sqref="B1" xr:uid="{00000000-0002-0000-0000-00000E000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select a period to highlight in H2. A Chart legend is in J2 to AI2" sqref="B2:F2" xr:uid="{00000000-0002-0000-0000-00000F000000}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup scale="51" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="44" fitToWidth="0" orientation="landscape" r:id="rId1"/>
   <headerFooter differentFirst="1">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>

--- a/Gantt chart.xlsx
+++ b/Gantt chart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gregory\Desktop\st_m1\Milestone1_Group52\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B20DDC-BEED-4215-ACAB-1A3CACE96739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D5EADC-55B5-4F65-84E3-A4A989D0450A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Planner" sheetId="1" r:id="rId1"/>
@@ -649,12 +649,33 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="9" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="10" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="10" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="10" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -675,27 +696,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="9" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="10" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -1112,7 +1112,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:67" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.85">
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="24" t="s">
         <v>46</v>
       </c>
       <c r="D1" s="10"/>
@@ -1121,11 +1121,11 @@
       <c r="G1" s="10"/>
     </row>
     <row r="2" spans="2:67" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
       <c r="G2" s="20" t="s">
         <v>11</v>
       </c>
@@ -1133,37 +1133,37 @@
         <v>1</v>
       </c>
       <c r="J2" s="12"/>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="27"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="34"/>
       <c r="P2" s="13"/>
-      <c r="Q2" s="25" t="s">
+      <c r="Q2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="27"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="34"/>
       <c r="U2" s="14"/>
-      <c r="V2" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="31"/>
+      <c r="V2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="38"/>
       <c r="Z2" s="15"/>
-      <c r="AA2" s="29" t="s">
+      <c r="AA2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="31"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="37"/>
+      <c r="AF2" s="37"/>
+      <c r="AG2" s="38"/>
       <c r="AH2" s="16"/>
       <c r="AI2" s="18" t="s">
         <v>3</v>
@@ -1177,22 +1177,22 @@
       <c r="AP2" s="19"/>
     </row>
     <row r="3" spans="2:67" s="9" customFormat="1" ht="39.950000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="31" t="s">
         <v>10</v>
       </c>
       <c r="H3" s="17" t="s">
@@ -1219,12 +1219,12 @@
       <c r="AA3" s="8"/>
     </row>
     <row r="4" spans="2:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="34"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
       <c r="H4" s="3">
         <v>1</v>
       </c>
@@ -1407,7 +1407,7 @@
       </c>
     </row>
     <row r="5" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="23" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="5">
@@ -1427,7 +1427,7 @@
       </c>
     </row>
     <row r="6" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="23" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="5">
@@ -1447,7 +1447,7 @@
       </c>
     </row>
     <row r="7" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="23" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="5">
@@ -1467,7 +1467,7 @@
       </c>
     </row>
     <row r="8" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="5">
@@ -1487,7 +1487,7 @@
       </c>
     </row>
     <row r="9" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="5">
@@ -1507,7 +1507,7 @@
       </c>
     </row>
     <row r="10" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="5">
@@ -1527,7 +1527,7 @@
       </c>
     </row>
     <row r="11" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="5">
@@ -1547,7 +1547,7 @@
       </c>
     </row>
     <row r="12" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="5">
@@ -1567,7 +1567,7 @@
       </c>
     </row>
     <row r="13" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="23" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="5">
@@ -1587,7 +1587,7 @@
       </c>
     </row>
     <row r="14" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="23" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="5">
@@ -1607,7 +1607,7 @@
       </c>
     </row>
     <row r="15" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="23" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="6">
@@ -1627,7 +1627,7 @@
       </c>
     </row>
     <row r="16" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="23" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="5">
@@ -1647,7 +1647,7 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="23" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="5">
@@ -1667,7 +1667,7 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="23" t="s">
         <v>26</v>
       </c>
       <c r="C18" s="5">
@@ -1687,7 +1687,7 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="23" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="5">
@@ -1707,7 +1707,7 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="23" t="s">
         <v>28</v>
       </c>
       <c r="C20" s="5">
@@ -1727,7 +1727,7 @@
       </c>
     </row>
     <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="23" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="5">
@@ -1747,7 +1747,7 @@
       </c>
     </row>
     <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="23" t="s">
         <v>30</v>
       </c>
       <c r="C22" s="5">
@@ -1767,7 +1767,7 @@
       </c>
     </row>
     <row r="23" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="23" t="s">
         <v>31</v>
       </c>
       <c r="C23" s="5">
@@ -1787,7 +1787,7 @@
       </c>
     </row>
     <row r="24" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="23" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="5">
@@ -1807,7 +1807,7 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="23" t="s">
         <v>33</v>
       </c>
       <c r="C25" s="5">
@@ -1827,7 +1827,7 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="36" t="s">
+      <c r="B26" s="23" t="s">
         <v>34</v>
       </c>
       <c r="C26" s="5">
@@ -1847,7 +1847,7 @@
       </c>
     </row>
     <row r="27" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="23" t="s">
         <v>35</v>
       </c>
       <c r="C27" s="5">
@@ -1867,7 +1867,7 @@
       </c>
     </row>
     <row r="28" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="23" t="s">
         <v>36</v>
       </c>
       <c r="C28" s="5">
@@ -1887,7 +1887,7 @@
       </c>
     </row>
     <row r="29" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="23" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="5">
@@ -1907,7 +1907,7 @@
       </c>
     </row>
     <row r="30" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="23" t="s">
         <v>38</v>
       </c>
       <c r="C30" s="5">
@@ -1927,7 +1927,7 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="36" t="s">
+      <c r="B31" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C31" s="5">
@@ -1936,14 +1936,18 @@
       <c r="D31" s="5">
         <v>14</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+      <c r="E31" s="5">
+        <v>15</v>
+      </c>
+      <c r="F31" s="5">
+        <v>16</v>
+      </c>
       <c r="G31" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="36" t="s">
+      <c r="B32" s="23" t="s">
         <v>40</v>
       </c>
       <c r="C32" s="5">
@@ -1952,14 +1956,18 @@
       <c r="D32" s="5">
         <v>6</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="E32" s="5">
+        <v>24</v>
+      </c>
+      <c r="F32" s="5">
+        <v>7</v>
+      </c>
       <c r="G32" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="36" t="s">
+      <c r="B33" s="23" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="5">
@@ -1968,14 +1976,18 @@
       <c r="D33" s="5">
         <v>4</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
+      <c r="E33" s="5">
+        <v>26</v>
+      </c>
+      <c r="F33" s="5">
+        <v>10</v>
+      </c>
       <c r="G33" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="36" t="s">
+      <c r="B34" s="23" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="5">
@@ -1988,14 +2000,14 @@
         <v>1</v>
       </c>
       <c r="F34" s="5">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G34" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="36" t="s">
+      <c r="B35" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="5">
@@ -2004,14 +2016,18 @@
       <c r="D35" s="5">
         <v>28</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="E35" s="5">
+        <v>23</v>
+      </c>
+      <c r="F35" s="5">
+        <v>17</v>
+      </c>
       <c r="G35" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="36" t="s">
+      <c r="B36" s="23" t="s">
         <v>44</v>
       </c>
       <c r="C36" s="5">
@@ -2020,14 +2036,18 @@
       <c r="D36" s="5">
         <v>4</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="E36" s="5">
+        <v>32</v>
+      </c>
+      <c r="F36" s="5">
+        <v>8</v>
+      </c>
       <c r="G36" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="36" t="s">
+      <c r="B37" s="23" t="s">
         <v>45</v>
       </c>
       <c r="C37" s="5">
@@ -2036,10 +2056,14 @@
       <c r="D37" s="5">
         <v>4</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="E37" s="5">
+        <v>36</v>
+      </c>
+      <c r="F37" s="5">
+        <v>4</v>
+      </c>
       <c r="G37" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2049,66 +2073,66 @@
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="21"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="38"/>
-      <c r="L38" s="38"/>
-      <c r="M38" s="38"/>
-      <c r="N38" s="38"/>
-      <c r="O38" s="38"/>
-      <c r="P38" s="38"/>
-      <c r="Q38" s="38"/>
-      <c r="R38" s="38"/>
-      <c r="S38" s="38"/>
-      <c r="T38" s="38"/>
-      <c r="U38" s="38"/>
-      <c r="V38" s="38"/>
-      <c r="W38" s="38"/>
-      <c r="X38" s="38"/>
-      <c r="Y38" s="38"/>
-      <c r="Z38" s="38"/>
-      <c r="AA38" s="38"/>
-      <c r="AB38" s="38"/>
-      <c r="AC38" s="38"/>
-      <c r="AD38" s="38"/>
-      <c r="AE38" s="38"/>
-      <c r="AF38" s="38"/>
-      <c r="AG38" s="38"/>
-      <c r="AH38" s="38"/>
-      <c r="AI38" s="38"/>
-      <c r="AJ38" s="38"/>
-      <c r="AK38" s="38"/>
-      <c r="AL38" s="38"/>
-      <c r="AM38" s="38"/>
-      <c r="AN38" s="38"/>
-      <c r="AO38" s="38"/>
-      <c r="AP38" s="38"/>
-      <c r="AQ38" s="38"/>
-      <c r="AR38" s="38"/>
-      <c r="AS38" s="38"/>
-      <c r="AT38" s="38"/>
-      <c r="AU38" s="38"/>
-      <c r="AV38" s="38"/>
-      <c r="AW38" s="38"/>
-      <c r="AX38" s="38"/>
-      <c r="AY38" s="38"/>
-      <c r="AZ38" s="38"/>
-      <c r="BA38" s="38"/>
-      <c r="BB38" s="38"/>
-      <c r="BC38" s="38"/>
-      <c r="BD38" s="38"/>
-      <c r="BE38" s="38"/>
-      <c r="BF38" s="38"/>
-      <c r="BG38" s="38"/>
-      <c r="BH38" s="38"/>
-      <c r="BI38" s="38"/>
-      <c r="BJ38" s="38"/>
-      <c r="BK38" s="38"/>
-      <c r="BL38" s="38"/>
-      <c r="BM38" s="38"/>
-      <c r="BN38" s="38"/>
-      <c r="BO38" s="38"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+      <c r="M38" s="25"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="25"/>
+      <c r="P38" s="25"/>
+      <c r="Q38" s="25"/>
+      <c r="R38" s="25"/>
+      <c r="S38" s="25"/>
+      <c r="T38" s="25"/>
+      <c r="U38" s="25"/>
+      <c r="V38" s="25"/>
+      <c r="W38" s="25"/>
+      <c r="X38" s="25"/>
+      <c r="Y38" s="25"/>
+      <c r="Z38" s="25"/>
+      <c r="AA38" s="25"/>
+      <c r="AB38" s="25"/>
+      <c r="AC38" s="25"/>
+      <c r="AD38" s="25"/>
+      <c r="AE38" s="25"/>
+      <c r="AF38" s="25"/>
+      <c r="AG38" s="25"/>
+      <c r="AH38" s="25"/>
+      <c r="AI38" s="25"/>
+      <c r="AJ38" s="25"/>
+      <c r="AK38" s="25"/>
+      <c r="AL38" s="25"/>
+      <c r="AM38" s="25"/>
+      <c r="AN38" s="25"/>
+      <c r="AO38" s="25"/>
+      <c r="AP38" s="25"/>
+      <c r="AQ38" s="25"/>
+      <c r="AR38" s="25"/>
+      <c r="AS38" s="25"/>
+      <c r="AT38" s="25"/>
+      <c r="AU38" s="25"/>
+      <c r="AV38" s="25"/>
+      <c r="AW38" s="25"/>
+      <c r="AX38" s="25"/>
+      <c r="AY38" s="25"/>
+      <c r="AZ38" s="25"/>
+      <c r="BA38" s="25"/>
+      <c r="BB38" s="25"/>
+      <c r="BC38" s="25"/>
+      <c r="BD38" s="25"/>
+      <c r="BE38" s="25"/>
+      <c r="BF38" s="25"/>
+      <c r="BG38" s="25"/>
+      <c r="BH38" s="25"/>
+      <c r="BI38" s="25"/>
+      <c r="BJ38" s="25"/>
+      <c r="BK38" s="25"/>
+      <c r="BL38" s="25"/>
+      <c r="BM38" s="25"/>
+      <c r="BN38" s="25"/>
+      <c r="BO38" s="25"/>
     </row>
     <row r="39" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="22"/>
@@ -2117,80 +2141,80 @@
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="21"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
-      <c r="J39" s="38"/>
-      <c r="K39" s="38"/>
-      <c r="L39" s="38"/>
-      <c r="M39" s="38"/>
-      <c r="N39" s="38"/>
-      <c r="O39" s="38"/>
-      <c r="P39" s="38"/>
-      <c r="Q39" s="38"/>
-      <c r="R39" s="38"/>
-      <c r="S39" s="38"/>
-      <c r="T39" s="38"/>
-      <c r="U39" s="38"/>
-      <c r="V39" s="38"/>
-      <c r="W39" s="38"/>
-      <c r="X39" s="38"/>
-      <c r="Y39" s="38"/>
-      <c r="Z39" s="38"/>
-      <c r="AA39" s="38"/>
-      <c r="AB39" s="38"/>
-      <c r="AC39" s="38"/>
-      <c r="AD39" s="38"/>
-      <c r="AE39" s="38"/>
-      <c r="AF39" s="38"/>
-      <c r="AG39" s="38"/>
-      <c r="AH39" s="38"/>
-      <c r="AI39" s="38"/>
-      <c r="AJ39" s="38"/>
-      <c r="AK39" s="38"/>
-      <c r="AL39" s="38"/>
-      <c r="AM39" s="38"/>
-      <c r="AN39" s="38"/>
-      <c r="AO39" s="38"/>
-      <c r="AP39" s="38"/>
-      <c r="AQ39" s="38"/>
-      <c r="AR39" s="38"/>
-      <c r="AS39" s="38"/>
-      <c r="AT39" s="38"/>
-      <c r="AU39" s="38"/>
-      <c r="AV39" s="38"/>
-      <c r="AW39" s="38"/>
-      <c r="AX39" s="38"/>
-      <c r="AY39" s="38"/>
-      <c r="AZ39" s="38"/>
-      <c r="BA39" s="38"/>
-      <c r="BB39" s="38"/>
-      <c r="BC39" s="38"/>
-      <c r="BD39" s="38"/>
-      <c r="BE39" s="38"/>
-      <c r="BF39" s="38"/>
-      <c r="BG39" s="38"/>
-      <c r="BH39" s="38"/>
-      <c r="BI39" s="38"/>
-      <c r="BJ39" s="38"/>
-      <c r="BK39" s="38"/>
-      <c r="BL39" s="38"/>
-      <c r="BM39" s="38"/>
-      <c r="BN39" s="38"/>
-      <c r="BO39" s="38"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+      <c r="M39" s="25"/>
+      <c r="N39" s="25"/>
+      <c r="O39" s="25"/>
+      <c r="P39" s="25"/>
+      <c r="Q39" s="25"/>
+      <c r="R39" s="25"/>
+      <c r="S39" s="25"/>
+      <c r="T39" s="25"/>
+      <c r="U39" s="25"/>
+      <c r="V39" s="25"/>
+      <c r="W39" s="25"/>
+      <c r="X39" s="25"/>
+      <c r="Y39" s="25"/>
+      <c r="Z39" s="25"/>
+      <c r="AA39" s="25"/>
+      <c r="AB39" s="25"/>
+      <c r="AC39" s="25"/>
+      <c r="AD39" s="25"/>
+      <c r="AE39" s="25"/>
+      <c r="AF39" s="25"/>
+      <c r="AG39" s="25"/>
+      <c r="AH39" s="25"/>
+      <c r="AI39" s="25"/>
+      <c r="AJ39" s="25"/>
+      <c r="AK39" s="25"/>
+      <c r="AL39" s="25"/>
+      <c r="AM39" s="25"/>
+      <c r="AN39" s="25"/>
+      <c r="AO39" s="25"/>
+      <c r="AP39" s="25"/>
+      <c r="AQ39" s="25"/>
+      <c r="AR39" s="25"/>
+      <c r="AS39" s="25"/>
+      <c r="AT39" s="25"/>
+      <c r="AU39" s="25"/>
+      <c r="AV39" s="25"/>
+      <c r="AW39" s="25"/>
+      <c r="AX39" s="25"/>
+      <c r="AY39" s="25"/>
+      <c r="AZ39" s="25"/>
+      <c r="BA39" s="25"/>
+      <c r="BB39" s="25"/>
+      <c r="BC39" s="25"/>
+      <c r="BD39" s="25"/>
+      <c r="BE39" s="25"/>
+      <c r="BF39" s="25"/>
+      <c r="BG39" s="25"/>
+      <c r="BH39" s="25"/>
+      <c r="BI39" s="25"/>
+      <c r="BJ39" s="25"/>
+      <c r="BK39" s="25"/>
+      <c r="BL39" s="25"/>
+      <c r="BM39" s="25"/>
+      <c r="BN39" s="25"/>
+      <c r="BO39" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="V2:Y2"/>
+    <mergeCell ref="AA2:AG2"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="K2:O2"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="V2:Y2"/>
-    <mergeCell ref="AA2:AG2"/>
   </mergeCells>
   <conditionalFormatting sqref="H4:BO4">
     <cfRule type="expression" dxfId="8" priority="8">
